--- a/feedback_forms/034_platform_promotion_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/034_platform_promotion_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>additional_comments_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Additional Comments 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>platform_promotions</t>
+          <t>platform_promotions_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Platform Promotions</t>
+          <t>Platform Promotions 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>platform_promotions_comments</t>
+          <t>platform_promotions_comments_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Platform Promotions Comments</t>
+          <t>Platform Promotions Comments 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1170,9 +1170,9 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'social',_'label':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Social', 'label': 'Social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'influencer',_'label':_'influencer'}</t>
+          <t>influencer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Influencer', 'label': 'Influencer'}</t>
+          <t>Influencer</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'affiliate',_'label':_'affiliate'}</t>
+          <t>affiliate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Affiliate', 'label': 'Affiliate'}</t>
+          <t>Affiliate</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'satisfied',_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Satisfied', 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_satisfied',_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Satisfied', 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Very Dissatisfied', 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'google',_'label':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Google', 'label': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'social',_'label':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Social', 'label': 'Social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'follow-up',_'label':_'follow-up'}</t>
+          <t>follow-up</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Follow-up', 'label': 'Follow-up'}</t>
+          <t>Follow-up</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sent',_'label':_'sent'}</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sent', 'label': 'Sent'}</t>
+          <t>Sent</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_sent',_'label':_'not_sent'}</t>
+          <t>not_sent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Sent', 'label': 'Not Sent'}</t>
+          <t>Not Sent</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'to_email',_'label':_'to_email'}</t>
+          <t>to_email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'To Email', 'label': 'To Email'}</t>
+          <t>To Email</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'from_email',_'label':_'from_email'}</t>
+          <t>from_email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'From Email', 'label': 'From Email'}</t>
+          <t>From Email</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chat',_'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Chat', 'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'in-app',_'label':_'in-app'}</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'In-app', 'label': 'In-app'}</t>
+          <t>In-app</t>
         </is>
       </c>
     </row>
@@ -1608,46 +1608,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>platform_promotions_choices</t>
+          <t>platform_promotions_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'google',_'label':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Google', 'label': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>platform_promotions_choices</t>
+          <t>platform_promotions_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'social',_'label':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Social', 'label': 'Social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
